--- a/artfynd/A 20312-2024 artfynd.xlsx
+++ b/artfynd/A 20312-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1104,6 +1104,1066 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122744255</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>gölen Ö, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>623052</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6876644</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122744201</v>
+      </c>
+      <c r="B6" t="n">
+        <v>74700</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kojan NÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>623441</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6876419</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122744688</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79645</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gulåsen N, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>623355</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6876467</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122744687</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79701</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gulåsen N, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>623355</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6876465</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122744686</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78694</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>185</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gulåsen N, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>623291</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6876520</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122744685</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gulåsen N, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>623100</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6876651</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122744205</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79741</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kojan NÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>623351</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6876470</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122744689</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79741</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gulåsen N, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>623359</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6876466</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122744690</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79645</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gulåsen N, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>623376</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6876456</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122744204</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79741</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kojan NÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>623358</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6876463</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20312-2024 artfynd.xlsx
+++ b/artfynd/A 20312-2024 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122744255</v>
+        <v>122744204</v>
       </c>
       <c r="B5" t="n">
-        <v>78660</v>
+        <v>79843</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1122,34 +1122,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>gölen Ö, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623052</v>
+        <v>623358</v>
       </c>
       <c r="R5" t="n">
-        <v>6876644</v>
+        <v>6876463</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122744201</v>
+        <v>122744687</v>
       </c>
       <c r="B6" t="n">
-        <v>74700</v>
+        <v>79803</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1228,34 +1228,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623441</v>
+        <v>623355</v>
       </c>
       <c r="R6" t="n">
-        <v>6876419</v>
+        <v>6876465</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1321,7 +1321,7 @@
         <v>122744688</v>
       </c>
       <c r="B7" t="n">
-        <v>79645</v>
+        <v>79747</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122744687</v>
+        <v>122744689</v>
       </c>
       <c r="B8" t="n">
-        <v>79701</v>
+        <v>79843</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1436,25 +1436,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623355</v>
+        <v>623359</v>
       </c>
       <c r="R8" t="n">
-        <v>6876465</v>
+        <v>6876466</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1530,10 +1530,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122744686</v>
+        <v>122744201</v>
       </c>
       <c r="B9" t="n">
-        <v>78694</v>
+        <v>74802</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,38 +1542,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623291</v>
+        <v>623441</v>
       </c>
       <c r="R9" t="n">
-        <v>6876520</v>
+        <v>6876419</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1636,10 +1636,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744685</v>
+        <v>122744686</v>
       </c>
       <c r="B10" t="n">
-        <v>78660</v>
+        <v>78796</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623100</v>
+        <v>623291</v>
       </c>
       <c r="R10" t="n">
-        <v>6876651</v>
+        <v>6876520</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744205</v>
+        <v>122744690</v>
       </c>
       <c r="B11" t="n">
-        <v>79741</v>
+        <v>79747</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,38 +1754,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623351</v>
+        <v>623376</v>
       </c>
       <c r="R11" t="n">
-        <v>6876470</v>
+        <v>6876456</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,12 +1812,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744689</v>
+        <v>122744685</v>
       </c>
       <c r="B12" t="n">
-        <v>79741</v>
+        <v>78762</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,21 +1864,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623359</v>
+        <v>623100</v>
       </c>
       <c r="R12" t="n">
-        <v>6876466</v>
+        <v>6876651</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122744690</v>
+        <v>122744255</v>
       </c>
       <c r="B13" t="n">
-        <v>79645</v>
+        <v>78762</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1966,38 +1966,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>gölen Ö, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623376</v>
+        <v>623052</v>
       </c>
       <c r="R13" t="n">
-        <v>6876456</v>
+        <v>6876644</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122744204</v>
+        <v>122744205</v>
       </c>
       <c r="B14" t="n">
-        <v>79741</v>
+        <v>79843</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623358</v>
+        <v>623351</v>
       </c>
       <c r="R14" t="n">
-        <v>6876463</v>
+        <v>6876470</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 20312-2024 artfynd.xlsx
+++ b/artfynd/A 20312-2024 artfynd.xlsx
@@ -1636,10 +1636,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744686</v>
+        <v>122744690</v>
       </c>
       <c r="B10" t="n">
-        <v>78796</v>
+        <v>79747</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,25 +1648,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623291</v>
+        <v>623376</v>
       </c>
       <c r="R10" t="n">
-        <v>6876520</v>
+        <v>6876456</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744690</v>
+        <v>122744685</v>
       </c>
       <c r="B11" t="n">
-        <v>79747</v>
+        <v>78762</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,25 +1754,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623376</v>
+        <v>623100</v>
       </c>
       <c r="R11" t="n">
-        <v>6876456</v>
+        <v>6876651</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744685</v>
+        <v>122744686</v>
       </c>
       <c r="B12" t="n">
-        <v>78762</v>
+        <v>78796</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,21 +1864,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623100</v>
+        <v>623291</v>
       </c>
       <c r="R12" t="n">
-        <v>6876651</v>
+        <v>6876520</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 20312-2024 artfynd.xlsx
+++ b/artfynd/A 20312-2024 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122744204</v>
+        <v>122744201</v>
       </c>
       <c r="B5" t="n">
-        <v>79843</v>
+        <v>74802</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1118,25 +1118,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623358</v>
+        <v>623441</v>
       </c>
       <c r="R5" t="n">
-        <v>6876463</v>
+        <v>6876419</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122744687</v>
+        <v>122744686</v>
       </c>
       <c r="B6" t="n">
-        <v>79803</v>
+        <v>78800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623355</v>
+        <v>623291</v>
       </c>
       <c r="R6" t="n">
-        <v>6876465</v>
+        <v>6876520</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122744688</v>
+        <v>122744205</v>
       </c>
       <c r="B7" t="n">
-        <v>79747</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1330,38 +1330,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623355</v>
+        <v>623351</v>
       </c>
       <c r="R7" t="n">
-        <v>6876467</v>
+        <v>6876470</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,7 +1427,7 @@
         <v>122744689</v>
       </c>
       <c r="B8" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1530,10 +1530,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122744201</v>
+        <v>122744687</v>
       </c>
       <c r="B9" t="n">
-        <v>74802</v>
+        <v>79807</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1546,34 +1546,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623441</v>
+        <v>623355</v>
       </c>
       <c r="R9" t="n">
-        <v>6876419</v>
+        <v>6876465</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,7 +1639,7 @@
         <v>122744690</v>
       </c>
       <c r="B10" t="n">
-        <v>79747</v>
+        <v>79751</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>122744685</v>
       </c>
       <c r="B11" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744686</v>
+        <v>122744688</v>
       </c>
       <c r="B12" t="n">
-        <v>78796</v>
+        <v>79751</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,25 +1860,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623291</v>
+        <v>623355</v>
       </c>
       <c r="R12" t="n">
-        <v>6876520</v>
+        <v>6876467</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122744255</v>
+        <v>122744204</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,34 +1970,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>gölen Ö, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623052</v>
+        <v>623358</v>
       </c>
       <c r="R13" t="n">
-        <v>6876644</v>
+        <v>6876463</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122744205</v>
+        <v>122744255</v>
       </c>
       <c r="B14" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,34 +2076,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>gölen Ö, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623351</v>
+        <v>623052</v>
       </c>
       <c r="R14" t="n">
-        <v>6876470</v>
+        <v>6876644</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 20312-2024 artfynd.xlsx
+++ b/artfynd/A 20312-2024 artfynd.xlsx
@@ -1636,10 +1636,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744690</v>
+        <v>122744685</v>
       </c>
       <c r="B10" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,25 +1648,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623376</v>
+        <v>623100</v>
       </c>
       <c r="R10" t="n">
-        <v>6876456</v>
+        <v>6876651</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744685</v>
+        <v>122744690</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,25 +1754,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623100</v>
+        <v>623376</v>
       </c>
       <c r="R11" t="n">
-        <v>6876651</v>
+        <v>6876456</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 20312-2024 artfynd.xlsx
+++ b/artfynd/A 20312-2024 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122744201</v>
+        <v>122744690</v>
       </c>
       <c r="B5" t="n">
-        <v>74802</v>
+        <v>79751</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1122,34 +1122,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623441</v>
+        <v>623376</v>
       </c>
       <c r="R5" t="n">
-        <v>6876419</v>
+        <v>6876456</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1212,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122744686</v>
+        <v>122744204</v>
       </c>
       <c r="B6" t="n">
-        <v>78800</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1228,34 +1228,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623291</v>
+        <v>623358</v>
       </c>
       <c r="R6" t="n">
-        <v>6876520</v>
+        <v>6876463</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122744205</v>
+        <v>122744255</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1334,34 +1334,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>gölen Ö, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623351</v>
+        <v>623052</v>
       </c>
       <c r="R7" t="n">
-        <v>6876470</v>
+        <v>6876644</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122744689</v>
+        <v>122744686</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>78800</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623359</v>
+        <v>623291</v>
       </c>
       <c r="R8" t="n">
-        <v>6876466</v>
+        <v>6876520</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1530,10 +1530,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122744687</v>
+        <v>122744689</v>
       </c>
       <c r="B9" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,25 +1542,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623355</v>
+        <v>623359</v>
       </c>
       <c r="R9" t="n">
-        <v>6876465</v>
+        <v>6876466</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744690</v>
+        <v>122744201</v>
       </c>
       <c r="B11" t="n">
-        <v>79751</v>
+        <v>74802</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,34 +1758,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623376</v>
+        <v>623441</v>
       </c>
       <c r="R11" t="n">
-        <v>6876456</v>
+        <v>6876419</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,12 +1812,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744688</v>
+        <v>122744205</v>
       </c>
       <c r="B12" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,38 +1860,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623355</v>
+        <v>623351</v>
       </c>
       <c r="R12" t="n">
-        <v>6876467</v>
+        <v>6876470</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,10 +1954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122744204</v>
+        <v>122744687</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1966,38 +1966,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623358</v>
+        <v>623355</v>
       </c>
       <c r="R13" t="n">
-        <v>6876463</v>
+        <v>6876465</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122744255</v>
+        <v>122744688</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2072,38 +2072,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>gölen Ö, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623052</v>
+        <v>623355</v>
       </c>
       <c r="R14" t="n">
-        <v>6876644</v>
+        <v>6876467</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,12 +2130,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 20312-2024 artfynd.xlsx
+++ b/artfynd/A 20312-2024 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122744690</v>
+        <v>122744689</v>
       </c>
       <c r="B5" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1118,25 +1118,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623376</v>
+        <v>623359</v>
       </c>
       <c r="R5" t="n">
-        <v>6876456</v>
+        <v>6876466</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122744204</v>
+        <v>122744201</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>74802</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623358</v>
+        <v>623441</v>
       </c>
       <c r="R6" t="n">
-        <v>6876463</v>
+        <v>6876419</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122744255</v>
+        <v>122744204</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1334,34 +1334,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>gölen Ö, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623052</v>
+        <v>623358</v>
       </c>
       <c r="R7" t="n">
-        <v>6876644</v>
+        <v>6876463</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122744686</v>
+        <v>122744687</v>
       </c>
       <c r="B8" t="n">
-        <v>78800</v>
+        <v>79807</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1436,25 +1436,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623291</v>
+        <v>623355</v>
       </c>
       <c r="R8" t="n">
-        <v>6876520</v>
+        <v>6876465</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1530,10 +1530,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122744689</v>
+        <v>122744685</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1546,21 +1546,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623359</v>
+        <v>623100</v>
       </c>
       <c r="R9" t="n">
-        <v>6876466</v>
+        <v>6876651</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744685</v>
+        <v>122744255</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1672,14 +1672,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>gölen Ö, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623100</v>
+        <v>623052</v>
       </c>
       <c r="R10" t="n">
-        <v>6876651</v>
+        <v>6876644</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744201</v>
+        <v>122744690</v>
       </c>
       <c r="B11" t="n">
-        <v>74802</v>
+        <v>79751</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,34 +1758,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623441</v>
+        <v>623376</v>
       </c>
       <c r="R11" t="n">
-        <v>6876419</v>
+        <v>6876456</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,12 +1812,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744205</v>
+        <v>122744686</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>78800</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,34 +1864,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623351</v>
+        <v>623291</v>
       </c>
       <c r="R12" t="n">
-        <v>6876470</v>
+        <v>6876520</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,10 +1954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122744687</v>
+        <v>122744205</v>
       </c>
       <c r="B13" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1966,38 +1966,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623355</v>
+        <v>623351</v>
       </c>
       <c r="R13" t="n">
-        <v>6876465</v>
+        <v>6876470</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 20312-2024 artfynd.xlsx
+++ b/artfynd/A 20312-2024 artfynd.xlsx
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122744204</v>
+        <v>122744687</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1330,38 +1330,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623358</v>
+        <v>623355</v>
       </c>
       <c r="R7" t="n">
-        <v>6876463</v>
+        <v>6876465</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122744687</v>
+        <v>122744204</v>
       </c>
       <c r="B8" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1436,38 +1436,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623355</v>
+        <v>623358</v>
       </c>
       <c r="R8" t="n">
-        <v>6876465</v>
+        <v>6876463</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 20312-2024 artfynd.xlsx
+++ b/artfynd/A 20312-2024 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122744689</v>
+        <v>122744255</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1122,34 +1122,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>gölen Ö, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623359</v>
+        <v>623052</v>
       </c>
       <c r="R5" t="n">
-        <v>6876466</v>
+        <v>6876644</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1212,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122744201</v>
+        <v>122744687</v>
       </c>
       <c r="B6" t="n">
-        <v>74802</v>
+        <v>79807</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1228,34 +1228,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623441</v>
+        <v>623355</v>
       </c>
       <c r="R6" t="n">
-        <v>6876419</v>
+        <v>6876465</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122744687</v>
+        <v>122744201</v>
       </c>
       <c r="B7" t="n">
-        <v>79807</v>
+        <v>74802</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1334,34 +1334,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623355</v>
+        <v>623441</v>
       </c>
       <c r="R7" t="n">
-        <v>6876465</v>
+        <v>6876419</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122744204</v>
+        <v>122744686</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>78800</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1440,34 +1440,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623358</v>
+        <v>623291</v>
       </c>
       <c r="R8" t="n">
-        <v>6876463</v>
+        <v>6876520</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,10 +1530,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122744685</v>
+        <v>122744689</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1546,21 +1546,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623100</v>
+        <v>623359</v>
       </c>
       <c r="R9" t="n">
-        <v>6876651</v>
+        <v>6876466</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744255</v>
+        <v>122744685</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1672,14 +1672,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>gölen Ö, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623052</v>
+        <v>623100</v>
       </c>
       <c r="R10" t="n">
-        <v>6876644</v>
+        <v>6876651</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744690</v>
+        <v>122744205</v>
       </c>
       <c r="B11" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,38 +1754,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623376</v>
+        <v>623351</v>
       </c>
       <c r="R11" t="n">
-        <v>6876456</v>
+        <v>6876470</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,12 +1812,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744686</v>
+        <v>122744690</v>
       </c>
       <c r="B12" t="n">
-        <v>78800</v>
+        <v>79751</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,25 +1860,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623291</v>
+        <v>623376</v>
       </c>
       <c r="R12" t="n">
-        <v>6876520</v>
+        <v>6876456</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122744205</v>
+        <v>122744688</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1966,38 +1966,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623351</v>
+        <v>623355</v>
       </c>
       <c r="R13" t="n">
-        <v>6876470</v>
+        <v>6876467</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122744688</v>
+        <v>122744204</v>
       </c>
       <c r="B14" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2072,38 +2072,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623355</v>
+        <v>623358</v>
       </c>
       <c r="R14" t="n">
-        <v>6876467</v>
+        <v>6876463</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,12 +2130,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 20312-2024 artfynd.xlsx
+++ b/artfynd/A 20312-2024 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122744255</v>
+        <v>122744690</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1118,38 +1118,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>gölen Ö, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623052</v>
+        <v>623376</v>
       </c>
       <c r="R5" t="n">
-        <v>6876644</v>
+        <v>6876456</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1212,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122744687</v>
+        <v>122744204</v>
       </c>
       <c r="B6" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1224,38 +1224,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623355</v>
+        <v>623358</v>
       </c>
       <c r="R6" t="n">
-        <v>6876465</v>
+        <v>6876463</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122744201</v>
+        <v>122744685</v>
       </c>
       <c r="B7" t="n">
-        <v>74802</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1330,38 +1330,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623441</v>
+        <v>623100</v>
       </c>
       <c r="R7" t="n">
-        <v>6876419</v>
+        <v>6876651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122744686</v>
+        <v>122744688</v>
       </c>
       <c r="B8" t="n">
-        <v>78800</v>
+        <v>79751</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1436,25 +1436,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623291</v>
+        <v>623355</v>
       </c>
       <c r="R8" t="n">
-        <v>6876520</v>
+        <v>6876467</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744685</v>
+        <v>122744255</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1672,14 +1672,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>gölen Ö, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623100</v>
+        <v>623052</v>
       </c>
       <c r="R10" t="n">
-        <v>6876651</v>
+        <v>6876644</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744205</v>
+        <v>122744201</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>74802</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,25 +1754,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623351</v>
+        <v>623441</v>
       </c>
       <c r="R11" t="n">
-        <v>6876470</v>
+        <v>6876419</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744690</v>
+        <v>122744686</v>
       </c>
       <c r="B12" t="n">
-        <v>79751</v>
+        <v>78800</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,25 +1860,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623376</v>
+        <v>623291</v>
       </c>
       <c r="R12" t="n">
-        <v>6876456</v>
+        <v>6876520</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122744688</v>
+        <v>122744205</v>
       </c>
       <c r="B13" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1966,38 +1966,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623355</v>
+        <v>623351</v>
       </c>
       <c r="R13" t="n">
-        <v>6876467</v>
+        <v>6876470</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122744204</v>
+        <v>122744687</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2072,38 +2072,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623358</v>
+        <v>623355</v>
       </c>
       <c r="R14" t="n">
-        <v>6876463</v>
+        <v>6876465</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,12 +2130,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 20312-2024 artfynd.xlsx
+++ b/artfynd/A 20312-2024 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122744690</v>
+        <v>122744685</v>
       </c>
       <c r="B5" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1118,25 +1118,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623376</v>
+        <v>623100</v>
       </c>
       <c r="R5" t="n">
-        <v>6876456</v>
+        <v>6876651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122744204</v>
+        <v>122744690</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1224,38 +1224,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623358</v>
+        <v>623376</v>
       </c>
       <c r="R6" t="n">
-        <v>6876463</v>
+        <v>6876456</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122744685</v>
+        <v>122744689</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1334,21 +1334,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623100</v>
+        <v>623359</v>
       </c>
       <c r="R7" t="n">
-        <v>6876651</v>
+        <v>6876466</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122744688</v>
+        <v>122744255</v>
       </c>
       <c r="B8" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1436,38 +1436,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>gölen Ö, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623355</v>
+        <v>623052</v>
       </c>
       <c r="R8" t="n">
-        <v>6876467</v>
+        <v>6876644</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,10 +1530,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122744689</v>
+        <v>122744688</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,25 +1542,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623359</v>
+        <v>623355</v>
       </c>
       <c r="R9" t="n">
-        <v>6876466</v>
+        <v>6876467</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1636,10 +1636,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744255</v>
+        <v>122744687</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>79807</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,38 +1648,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>gölen Ö, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623052</v>
+        <v>623355</v>
       </c>
       <c r="R10" t="n">
-        <v>6876644</v>
+        <v>6876465</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1851,7 +1851,7 @@
         <v>122744686</v>
       </c>
       <c r="B12" t="n">
-        <v>78800</v>
+        <v>78798</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122744687</v>
+        <v>122744204</v>
       </c>
       <c r="B14" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2072,38 +2072,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623355</v>
+        <v>623358</v>
       </c>
       <c r="R14" t="n">
-        <v>6876465</v>
+        <v>6876463</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,12 +2130,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 20312-2024 artfynd.xlsx
+++ b/artfynd/A 20312-2024 artfynd.xlsx
@@ -1424,10 +1424,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122744255</v>
+        <v>122744687</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>79807</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1436,38 +1436,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>gölen Ö, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623052</v>
+        <v>623355</v>
       </c>
       <c r="R8" t="n">
-        <v>6876644</v>
+        <v>6876465</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,10 +1530,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122744688</v>
+        <v>122744255</v>
       </c>
       <c r="B9" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,38 +1542,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>gölen Ö, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623355</v>
+        <v>623052</v>
       </c>
       <c r="R9" t="n">
-        <v>6876467</v>
+        <v>6876644</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1636,10 +1636,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744687</v>
+        <v>122744688</v>
       </c>
       <c r="B10" t="n">
-        <v>79807</v>
+        <v>79751</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1679,7 +1679,7 @@
         <v>623355</v>
       </c>
       <c r="R10" t="n">
-        <v>6876465</v>
+        <v>6876467</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 20312-2024 artfynd.xlsx
+++ b/artfynd/A 20312-2024 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122744685</v>
+        <v>122744201</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>74802</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1118,38 +1118,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623100</v>
+        <v>623441</v>
       </c>
       <c r="R5" t="n">
-        <v>6876651</v>
+        <v>6876419</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1212,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122744690</v>
+        <v>122744687</v>
       </c>
       <c r="B6" t="n">
-        <v>79751</v>
+        <v>79807</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1228,21 +1228,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623376</v>
+        <v>623355</v>
       </c>
       <c r="R6" t="n">
-        <v>6876456</v>
+        <v>6876465</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122744689</v>
+        <v>122744685</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1334,21 +1334,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623359</v>
+        <v>623100</v>
       </c>
       <c r="R7" t="n">
-        <v>6876466</v>
+        <v>6876651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122744687</v>
+        <v>122744205</v>
       </c>
       <c r="B8" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1436,38 +1436,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623355</v>
+        <v>623351</v>
       </c>
       <c r="R8" t="n">
-        <v>6876465</v>
+        <v>6876470</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,10 +1530,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122744255</v>
+        <v>122744204</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1546,34 +1546,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>gölen Ö, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623052</v>
+        <v>623358</v>
       </c>
       <c r="R9" t="n">
-        <v>6876644</v>
+        <v>6876463</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1636,10 +1636,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744688</v>
+        <v>122744686</v>
       </c>
       <c r="B10" t="n">
-        <v>79751</v>
+        <v>78798</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,25 +1648,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623355</v>
+        <v>623291</v>
       </c>
       <c r="R10" t="n">
-        <v>6876467</v>
+        <v>6876520</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744201</v>
+        <v>122744690</v>
       </c>
       <c r="B11" t="n">
-        <v>74802</v>
+        <v>79751</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,34 +1758,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623441</v>
+        <v>623376</v>
       </c>
       <c r="R11" t="n">
-        <v>6876419</v>
+        <v>6876456</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,12 +1812,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744686</v>
+        <v>122744688</v>
       </c>
       <c r="B12" t="n">
-        <v>78798</v>
+        <v>79751</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,25 +1860,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623291</v>
+        <v>623355</v>
       </c>
       <c r="R12" t="n">
-        <v>6876520</v>
+        <v>6876467</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,7 +1954,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122744205</v>
+        <v>122744689</v>
       </c>
       <c r="B13" t="n">
         <v>79847</v>
@@ -1990,14 +1990,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623351</v>
+        <v>623359</v>
       </c>
       <c r="R13" t="n">
-        <v>6876470</v>
+        <v>6876466</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122744204</v>
+        <v>122744255</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,34 +2076,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>gölen Ö, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623358</v>
+        <v>623052</v>
       </c>
       <c r="R14" t="n">
-        <v>6876463</v>
+        <v>6876644</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 20312-2024 artfynd.xlsx
+++ b/artfynd/A 20312-2024 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122744201</v>
+        <v>122744686</v>
       </c>
       <c r="B5" t="n">
-        <v>74802</v>
+        <v>78798</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1118,38 +1118,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623441</v>
+        <v>623291</v>
       </c>
       <c r="R5" t="n">
-        <v>6876419</v>
+        <v>6876520</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1212,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122744687</v>
+        <v>122744205</v>
       </c>
       <c r="B6" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1224,38 +1224,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623355</v>
+        <v>623351</v>
       </c>
       <c r="R6" t="n">
-        <v>6876465</v>
+        <v>6876470</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122744205</v>
+        <v>122744687</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1436,38 +1436,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623351</v>
+        <v>623355</v>
       </c>
       <c r="R8" t="n">
-        <v>6876470</v>
+        <v>6876465</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,7 +1530,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122744204</v>
+        <v>122744689</v>
       </c>
       <c r="B9" t="n">
         <v>79847</v>
@@ -1566,14 +1566,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623358</v>
+        <v>623359</v>
       </c>
       <c r="R9" t="n">
-        <v>6876463</v>
+        <v>6876466</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1636,10 +1636,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744686</v>
+        <v>122744688</v>
       </c>
       <c r="B10" t="n">
-        <v>78798</v>
+        <v>79751</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,25 +1648,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623291</v>
+        <v>623355</v>
       </c>
       <c r="R10" t="n">
-        <v>6876520</v>
+        <v>6876467</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744690</v>
+        <v>122744255</v>
       </c>
       <c r="B11" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,38 +1754,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>gölen Ö, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623376</v>
+        <v>623052</v>
       </c>
       <c r="R11" t="n">
-        <v>6876456</v>
+        <v>6876644</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,12 +1812,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744688</v>
+        <v>122744201</v>
       </c>
       <c r="B12" t="n">
-        <v>79751</v>
+        <v>74802</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,34 +1864,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623355</v>
+        <v>623441</v>
       </c>
       <c r="R12" t="n">
-        <v>6876467</v>
+        <v>6876419</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,7 +1954,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122744689</v>
+        <v>122744204</v>
       </c>
       <c r="B13" t="n">
         <v>79847</v>
@@ -1990,14 +1990,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623359</v>
+        <v>623358</v>
       </c>
       <c r="R13" t="n">
-        <v>6876466</v>
+        <v>6876463</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122744255</v>
+        <v>122744690</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2072,38 +2072,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>gölen Ö, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623052</v>
+        <v>623376</v>
       </c>
       <c r="R14" t="n">
-        <v>6876644</v>
+        <v>6876456</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,12 +2130,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 20312-2024 artfynd.xlsx
+++ b/artfynd/A 20312-2024 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122744686</v>
+        <v>122744685</v>
       </c>
       <c r="B5" t="n">
-        <v>78798</v>
+        <v>78769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1122,21 +1122,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623291</v>
+        <v>623100</v>
       </c>
       <c r="R5" t="n">
-        <v>6876520</v>
+        <v>6876651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1212,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122744205</v>
+        <v>122744689</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1248,14 +1248,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623351</v>
+        <v>623359</v>
       </c>
       <c r="R6" t="n">
-        <v>6876470</v>
+        <v>6876466</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122744685</v>
+        <v>122744255</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1354,14 +1354,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>gölen Ö, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623100</v>
+        <v>623052</v>
       </c>
       <c r="R7" t="n">
-        <v>6876651</v>
+        <v>6876644</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122744687</v>
+        <v>122744688</v>
       </c>
       <c r="B8" t="n">
-        <v>79807</v>
+        <v>79754</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1467,7 +1467,7 @@
         <v>623355</v>
       </c>
       <c r="R8" t="n">
-        <v>6876465</v>
+        <v>6876467</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1530,10 +1530,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122744689</v>
+        <v>122744205</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1566,14 +1566,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623359</v>
+        <v>623351</v>
       </c>
       <c r="R9" t="n">
-        <v>6876466</v>
+        <v>6876470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1636,10 +1636,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744688</v>
+        <v>122744204</v>
       </c>
       <c r="B10" t="n">
-        <v>79751</v>
+        <v>79850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,38 +1648,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623355</v>
+        <v>623358</v>
       </c>
       <c r="R10" t="n">
-        <v>6876467</v>
+        <v>6876463</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1742,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744255</v>
+        <v>122744686</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>78801</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,34 +1758,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>gölen Ö, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623052</v>
+        <v>623291</v>
       </c>
       <c r="R11" t="n">
-        <v>6876644</v>
+        <v>6876520</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,12 +1812,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744201</v>
+        <v>122744687</v>
       </c>
       <c r="B12" t="n">
-        <v>74802</v>
+        <v>79810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,34 +1864,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623441</v>
+        <v>623355</v>
       </c>
       <c r="R12" t="n">
-        <v>6876419</v>
+        <v>6876465</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1954,10 +1954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122744204</v>
+        <v>122744201</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>74805</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1966,25 +1966,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623358</v>
+        <v>623441</v>
       </c>
       <c r="R13" t="n">
-        <v>6876463</v>
+        <v>6876419</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2063,7 +2063,7 @@
         <v>122744690</v>
       </c>
       <c r="B14" t="n">
-        <v>79751</v>
+        <v>79754</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 20312-2024 artfynd.xlsx
+++ b/artfynd/A 20312-2024 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122744685</v>
+        <v>122744255</v>
       </c>
       <c r="B5" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1142,14 +1142,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>gölen Ö, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623100</v>
+        <v>623052</v>
       </c>
       <c r="R5" t="n">
-        <v>6876651</v>
+        <v>6876644</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1212,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122744689</v>
+        <v>122744201</v>
       </c>
       <c r="B6" t="n">
-        <v>79850</v>
+        <v>74805</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1224,38 +1224,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623359</v>
+        <v>623441</v>
       </c>
       <c r="R6" t="n">
-        <v>6876466</v>
+        <v>6876419</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122744255</v>
+        <v>122744685</v>
       </c>
       <c r="B7" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1354,14 +1354,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>gölen Ö, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623052</v>
+        <v>623100</v>
       </c>
       <c r="R7" t="n">
-        <v>6876644</v>
+        <v>6876651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,7 +1427,7 @@
         <v>122744688</v>
       </c>
       <c r="B8" t="n">
-        <v>79754</v>
+        <v>79756</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1530,10 +1530,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122744205</v>
+        <v>122744690</v>
       </c>
       <c r="B9" t="n">
-        <v>79850</v>
+        <v>79756</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,38 +1542,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623351</v>
+        <v>623376</v>
       </c>
       <c r="R9" t="n">
-        <v>6876470</v>
+        <v>6876456</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1636,10 +1636,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744204</v>
+        <v>122744205</v>
       </c>
       <c r="B10" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623358</v>
+        <v>623351</v>
       </c>
       <c r="R10" t="n">
-        <v>6876463</v>
+        <v>6876470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1742,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744686</v>
+        <v>122744687</v>
       </c>
       <c r="B11" t="n">
-        <v>78801</v>
+        <v>79812</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,25 +1754,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623291</v>
+        <v>623355</v>
       </c>
       <c r="R11" t="n">
-        <v>6876520</v>
+        <v>6876465</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744687</v>
+        <v>122744204</v>
       </c>
       <c r="B12" t="n">
-        <v>79810</v>
+        <v>79852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,38 +1860,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gulåsen N, Hls</t>
+          <t>Kojan NÖ, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623355</v>
+        <v>623358</v>
       </c>
       <c r="R12" t="n">
-        <v>6876465</v>
+        <v>6876463</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1954,10 +1954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122744201</v>
+        <v>122744689</v>
       </c>
       <c r="B13" t="n">
-        <v>74805</v>
+        <v>79852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1966,38 +1966,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kojan NÖ, Hls</t>
+          <t>Gulåsen N, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623441</v>
+        <v>623359</v>
       </c>
       <c r="R13" t="n">
-        <v>6876419</v>
+        <v>6876466</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2060,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122744690</v>
+        <v>122744686</v>
       </c>
       <c r="B14" t="n">
-        <v>79754</v>
+        <v>78803</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2072,25 +2072,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623376</v>
+        <v>623291</v>
       </c>
       <c r="R14" t="n">
-        <v>6876456</v>
+        <v>6876520</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
